--- a/DÍA 4/Matrices+Desbordadas.xlsx
+++ b/DÍA 4/Matrices+Desbordadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUSTAVO\Documents\Cursos Udemy\ExcelTotal\DÍA 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC86AF88-48BA-4843-8641-EEC2F8CB2693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D69010-70BE-4FED-8F08-E844B0516282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{02A90A6A-D7B6-4A56-B81F-18FCC99E18C9}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -88,10 +88,10 @@
     <t>Benito</t>
   </si>
   <si>
-    <t>uso la fórumula ordenar</t>
-  </si>
-  <si>
     <t>LAS MATRICES DESBORDADAS NO FUNCIONAN EN LAS TABLAS. ME MUESTRAN UN RANGO DE VALORES. PODES HACER MATRICES DESBORDADS DE UNA HOJA A OTRA O DE UN LIBRO A OTRO LIBRO. LOS DOS LIBROS TIENEN QUE ESTAR ABIERTOS PARA QUE FUNCIONE.</t>
+  </si>
+  <si>
+    <t>Uso la fórmula ordenar</t>
   </si>
 </sst>
 </file>
@@ -490,11 +490,11 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
